--- a/data/trans_orig/IP25-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45328</t>
+          <t>45226</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61294</t>
+          <t>61379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47025</t>
+          <t>47167</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64044</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96921</t>
+          <t>97198</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122157</t>
+          <t>121923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,75%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44166</t>
+          <t>44081</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60132</t>
+          <t>60234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>56178</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74355</t>
+          <t>74213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104683</t>
+          <t>104917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129919</t>
+          <t>129642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,15%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>242203</t>
+          <t>241589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>249580</t>
+          <t>249705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>236725</t>
+          <t>236588</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>246991</t>
+          <t>246729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>481845</t>
+          <t>481252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>494767</t>
+          <t>494314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17031</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12194</t>
+          <t>12647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25116</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121407</t>
+          <t>121356</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126908</t>
+          <t>126904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129284</t>
+          <t>129889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138107</t>
+          <t>138117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>254321</t>
+          <t>253926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264196</t>
+          <t>264296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>15137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>183542</t>
+          <t>183297</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>190906</t>
+          <t>190909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>194704</t>
+          <t>194287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202808</t>
+          <t>202977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>381875</t>
+          <t>380721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>392362</t>
+          <t>392240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>18692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>601092</t>
+          <t>600298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>625225</t>
+          <t>625132</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>616993</t>
+          <t>616543</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>645702</t>
+          <t>645662</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1227233</t>
+          <t>1227346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1264402</t>
+          <t>1263383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54352</t>
+          <t>54445</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78485</t>
+          <t>79279</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76998</t>
+          <t>77038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105707</t>
+          <t>106157</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137875</t>
+          <t>138894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175044</t>
+          <t>174931</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72262</t>
+          <t>72453</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92641</t>
+          <t>91727</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77840</t>
+          <t>77386</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96764</t>
+          <t>97219</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>156177</t>
+          <t>155726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>183263</t>
+          <t>183067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53178</t>
+          <t>54092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73557</t>
+          <t>73366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46201</t>
+          <t>45746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65125</t>
+          <t>65579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105521</t>
+          <t>105717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132607</t>
+          <t>133058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>223881</t>
+          <t>223025</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>232399</t>
+          <t>231926</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>261940</t>
+          <t>262065</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>268306</t>
+          <t>268315</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>488364</t>
+          <t>488598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>499156</t>
+          <t>499490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150504</t>
+          <t>150517</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156345</t>
+          <t>156347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151056</t>
+          <t>151333</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157252</t>
+          <t>157884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>304624</t>
+          <t>304806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>312882</t>
+          <t>312911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162481</t>
+          <t>162304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169453</t>
+          <t>169432</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,49 +3723,49 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>175535</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>170364</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>177973</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>94,67%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>98,9%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>175535</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>170581</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>178135</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>94,79%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>496</t>
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>335808</t>
+          <t>336381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>346380</t>
+          <t>346645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,47 +3836,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4420</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9591</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4420</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1820</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9374</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>617612</t>
+          <t>618615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>645912</t>
+          <t>646696</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>672442</t>
+          <t>670650</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>697686</t>
+          <t>697623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1299481</t>
+          <t>1298862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1335811</t>
+          <t>1337184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64538</t>
+          <t>63754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92838</t>
+          <t>91835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52796</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78040</t>
+          <t>79832</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125120</t>
+          <t>123747</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>161450</t>
+          <t>162069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64566</t>
+          <t>64752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82171</t>
+          <t>82313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69211</t>
+          <t>69430</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86584</t>
+          <t>86831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139047</t>
+          <t>137228</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163178</t>
+          <t>163605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,95%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49483</t>
+          <t>49341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67088</t>
+          <t>66902</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37580</t>
+          <t>37333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54953</t>
+          <t>54734</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92640</t>
+          <t>92213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116771</t>
+          <t>118590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200725</t>
+          <t>201106</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208424</t>
+          <t>208564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>244509</t>
+          <t>244778</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>253519</t>
+          <t>253554</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>449227</t>
+          <t>449075</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>460593</t>
+          <t>460761</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13552</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177934</t>
+          <t>178149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186375</t>
+          <t>186096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>181725</t>
+          <t>181579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>187953</t>
+          <t>187954</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>363424</t>
+          <t>362448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373341</t>
+          <t>373275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166016</t>
+          <t>166098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172130</t>
+          <t>172125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160823</t>
+          <t>161293</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170135</t>
+          <t>170314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>330087</t>
+          <t>329750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>341137</t>
+          <t>341212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>12755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>618103</t>
+          <t>618652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>644853</t>
+          <t>644628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>666379</t>
+          <t>666188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>691435</t>
+          <t>691607</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1292026</t>
+          <t>1294340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1329840</t>
+          <t>1330065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59518</t>
+          <t>59743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86268</t>
+          <t>85719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>53237</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78465</t>
+          <t>78656</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119375</t>
+          <t>119150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>157189</t>
+          <t>154875</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
